--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 26 недель не входят и идут до них.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 13 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -642,209 +642,254 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46451</v>
+        <v>46360</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Дата начала + 26 недель, последний рабочий день</t>
+          <t>Дата начала + 13 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Трудозатраты, ч-д</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>26 недель × 5 рабочих дней. План предполагает одного инженера на полной занятости.</t>
+          <t>Сумма по этапам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>11515</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Этапы 1–7. Помещается в 13 недель × 5 дней = 65 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>B8*B9</f>
-        <v>1496950</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Этапы 8–9 (консолидация мелких АТС и перенумерация) — работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером 85 ч-д за 13 недель не выполняются, это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>11515</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Оборудование (4 сервера) проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>B8*B11</f>
+        <v>978775</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Сервер под московский узел проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8</v>
+        <v>1255</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7 региональных узлов + резервный мастер</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>8 узлов + арбитр без данных</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Новогодние каникулы</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>неделя 18</t>
-        </is>
+          <t>Узлов кластера после внедрения</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. При старте 07.09.2026 неделя 18 приходится на 04–08.01.2027, то есть на нерабочие дни. Сроки в плане календарные и этого не учитывают. Либо сдвиньте дату начала, либо считайте план 27-недельным: этапы 8 и 9 (консолидация и перенумерация) в эту неделю не ведутся.</t>
+          <t>Ростов (мастер) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Голосов в кворуме</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Пять узлов, число нечётное — отдельный арбитр не нужен. Кластер переживает потерю двух узлов из пяти.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Серверов нужно докупить</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера. Четыре площадки уже имеют свои машины, новый сервер нужен только под Москву. Ставрополь (74 абонента) остаётся на ростовском сервере, как сейчас.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Резервный мастер отдельной машиной</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Пятый сервер занят московским узлом. Отдельная машина под тёплый резерв не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел. Процедура отрабатывается на этапе 7 учебно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Инженер проекта и ответственные за стадии. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -861,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:AJ18"/>
+  <dimension ref="C1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.699999999999999" customWidth="1" min="1" max="1"/>
@@ -887,19 +932,6 @@
     <col width="3.9" customWidth="1" min="21" max="21"/>
     <col width="3.9" customWidth="1" min="22" max="22"/>
     <col width="3.9" customWidth="1" min="23" max="23"/>
-    <col width="3.9" customWidth="1" min="24" max="24"/>
-    <col width="3.9" customWidth="1" min="25" max="25"/>
-    <col width="3.9" customWidth="1" min="26" max="26"/>
-    <col width="3.9" customWidth="1" min="27" max="27"/>
-    <col width="3.9" customWidth="1" min="28" max="28"/>
-    <col width="3.9" customWidth="1" min="29" max="29"/>
-    <col width="3.9" customWidth="1" min="30" max="30"/>
-    <col width="3.9" customWidth="1" min="31" max="31"/>
-    <col width="3.9" customWidth="1" min="32" max="32"/>
-    <col width="3.9" customWidth="1" min="33" max="33"/>
-    <col width="3.9" customWidth="1" min="34" max="34"/>
-    <col width="3.9" customWidth="1" min="35" max="35"/>
-    <col width="3.9" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -958,26 +990,6 @@
           <t>Ноябрь 2026</t>
         </is>
       </c>
-      <c r="X1" s="12" t="inlineStr">
-        <is>
-          <t>Декабрь 2026</t>
-        </is>
-      </c>
-      <c r="AB1" s="12" t="inlineStr">
-        <is>
-          <t>Январь 2027</t>
-        </is>
-      </c>
-      <c r="AF1" s="12" t="inlineStr">
-        <is>
-          <t>Февраль 2027</t>
-        </is>
-      </c>
-      <c r="AJ1" s="12" t="inlineStr">
-        <is>
-          <t>Март 2027</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="K2" s="13" t="inlineStr">
@@ -1045,71 +1057,6 @@
           <t>30-06</t>
         </is>
       </c>
-      <c r="X2" s="13" t="inlineStr">
-        <is>
-          <t>07-13</t>
-        </is>
-      </c>
-      <c r="Y2" s="13" t="inlineStr">
-        <is>
-          <t>14-20</t>
-        </is>
-      </c>
-      <c r="Z2" s="13" t="inlineStr">
-        <is>
-          <t>21-27</t>
-        </is>
-      </c>
-      <c r="AA2" s="13" t="inlineStr">
-        <is>
-          <t>28-03</t>
-        </is>
-      </c>
-      <c r="AB2" s="13" t="inlineStr">
-        <is>
-          <t>04-10</t>
-        </is>
-      </c>
-      <c r="AC2" s="13" t="inlineStr">
-        <is>
-          <t>11-17</t>
-        </is>
-      </c>
-      <c r="AD2" s="13" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-      <c r="AE2" s="13" t="inlineStr">
-        <is>
-          <t>25-31</t>
-        </is>
-      </c>
-      <c r="AF2" s="13" t="inlineStr">
-        <is>
-          <t>01-07</t>
-        </is>
-      </c>
-      <c r="AG2" s="13" t="inlineStr">
-        <is>
-          <t>08-14</t>
-        </is>
-      </c>
-      <c r="AH2" s="13" t="inlineStr">
-        <is>
-          <t>15-21</t>
-        </is>
-      </c>
-      <c r="AI2" s="13" t="inlineStr">
-        <is>
-          <t>22-28</t>
-        </is>
-      </c>
-      <c r="AJ2" s="13" t="inlineStr">
-        <is>
-          <t>01-07</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="C3" s="14" t="inlineStr">
@@ -1119,7 +1066,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>07.09.26 - 05.03.27</t>
+          <t>07.09.26 - 04.12.26</t>
         </is>
       </c>
       <c r="E3" s="15" t="n"/>
@@ -1136,7 +1083,7 @@
       <c r="H3" s="15" t="n"/>
       <c r="I3" s="14">
         <f>SUM(I4:I12)</f>
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
@@ -1156,19 +1103,6 @@
       <c r="U3" s="16" t="n"/>
       <c r="V3" s="16" t="n"/>
       <c r="W3" s="16" t="n"/>
-      <c r="X3" s="16" t="n"/>
-      <c r="Y3" s="16" t="n"/>
-      <c r="Z3" s="16" t="n"/>
-      <c r="AA3" s="16" t="n"/>
-      <c r="AB3" s="16" t="n"/>
-      <c r="AC3" s="16" t="n"/>
-      <c r="AD3" s="16" t="n"/>
-      <c r="AE3" s="16" t="n"/>
-      <c r="AF3" s="16" t="n"/>
-      <c r="AG3" s="16" t="n"/>
-      <c r="AH3" s="16" t="n"/>
-      <c r="AI3" s="16" t="n"/>
-      <c r="AJ3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="17" t="n"/>
@@ -1186,16 +1120,15 @@
       </c>
       <c r="H4" s="18" t="n"/>
       <c r="I4" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>RTT выше 50 мс до региона — регион не включается в синхронную репликацию, получает автономную АТС с транком. Отсутствие IP у Славянска-на-Кубани и локального PBX блокирует недели 11 и 15. Оператор может не дать отдельных пользователей ВАТС — тогда площадка работает через мастер.</t>
+          <t>RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию, получает автономную АТС с транком. Отсутствие IP у Славянска-на-Кубани и локального PBX блокирует недели 8 и 12. Оператор может не дать отдельных пользователей ВАТС — тогда площадка работает через мастер.</t>
         </is>
       </c>
       <c r="K4" s="16" t="n"/>
       <c r="L4" s="16" t="n"/>
-      <c r="M4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="17" t="n"/>
@@ -1213,11 +1146,11 @@
       </c>
       <c r="H5" s="18" t="n"/>
       <c r="I5" s="17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="16" t="n"/>
       <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="17" t="n"/>
@@ -1235,11 +1168,10 @@
       </c>
       <c r="H6" s="18" t="n"/>
       <c r="I6" s="17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J6" s="17" t="inlineStr"/>
       <c r="M6" s="16" t="n"/>
-      <c r="N6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="17" t="n"/>
@@ -1257,15 +1189,14 @@
       </c>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Требуется окно на перезапуск базы: новые вызовы не устанавливаются около минуты.</t>
         </is>
       </c>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="17" t="n"/>
@@ -1283,16 +1214,15 @@
       </c>
       <c r="H8" s="18" t="n"/>
       <c r="I8" s="17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>Контрольная точка: при проблемах на Воронеже тиражирование не начинается, пока они не закрыты. Пауза заложена в план.</t>
-        </is>
-      </c>
+          <t>Контрольная точка: при проблемах на Воронеже тиражирование не начинается, пока они не закрыты. При сжатом сроке это единственный запас в плане — сдвиг здесь двигает весь график.</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="n"/>
       <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="17" t="n"/>
@@ -1300,7 +1230,7 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>6. Тиражирование на пять площадок</t>
+          <t>6. Тиражирование на три площадки</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -1310,20 +1240,16 @@
       </c>
       <c r="H9" s="18" t="n"/>
       <c r="I9" s="17" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>Узлы перезапускаются по одному, работы по площадкам не совмещаются. Регион 5 в исходных данных назван «Москва, СПб, Новосибирск» — при реальном размещении в Новосибирске регион исключается из синхронной репликации.</t>
-        </is>
-      </c>
+          <t>Узлы перевводятся по одному, работы по площадкам не совмещаются. Регион 5 в исходных данных назван «Москва, СПб, Новосибирск» — при реальном размещении абонентов в Новосибирске площадка исключается из синхронной репликации.</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
       <c r="S9" s="16" t="n"/>
-      <c r="T9" s="16" t="n"/>
-      <c r="U9" s="16" t="n"/>
-      <c r="V9" s="16" t="n"/>
-      <c r="W9" s="16" t="n"/>
-      <c r="X9" s="16" t="n"/>
-      <c r="Y9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="17" t="n"/>
@@ -1331,7 +1257,7 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>7. Резервный мастер</t>
+          <t>7. Учебная передача роли мастера</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -1341,10 +1267,14 @@
       </c>
       <c r="H10" s="18" t="n"/>
       <c r="I10" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="Z10" s="16" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>Отдельной машины под резервный мастер нет: роль передаётся на один из рабочих узлов. Процедура обязана быть опробована заранее, иначе в аварию не сработает.</t>
+        </is>
+      </c>
+      <c r="T10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="17" t="n"/>
@@ -1352,7 +1282,7 @@
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>8. Консолидация семи мелких АТС</t>
+          <t>8. Консолидация мелких АТС</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -1362,18 +1292,16 @@
       </c>
       <c r="H11" s="18" t="n"/>
       <c r="I11" s="17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J11" s="17" t="inlineStr"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
+      <c r="U11" s="16" t="n"/>
       <c r="V11" s="16" t="n"/>
-      <c r="W11" s="16" t="n"/>
-      <c r="X11" s="16" t="n"/>
-      <c r="Y11" s="16" t="n"/>
-      <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="16" t="n"/>
-      <c r="AC11" s="16" t="n"/>
-      <c r="AD11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="17" t="n"/>
@@ -1391,13 +1319,14 @@
       </c>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>Организационный поток: новые площадки не заводятся до разведения конфликтов нумерации. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
-        </is>
-      </c>
+          <t>Организационный поток, идёт силами второго исполнителя. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="n"/>
       <c r="P12" s="16" t="n"/>
       <c r="Q12" s="16" t="n"/>
       <c r="R12" s="16" t="n"/>
@@ -1406,19 +1335,6 @@
       <c r="U12" s="16" t="n"/>
       <c r="V12" s="16" t="n"/>
       <c r="W12" s="16" t="n"/>
-      <c r="X12" s="16" t="n"/>
-      <c r="Y12" s="16" t="n"/>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="16" t="n"/>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="16" t="n"/>
-      <c r="AH12" s="16" t="n"/>
-      <c r="AI12" s="16" t="n"/>
-      <c r="AJ12" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="F15" s="7" t="inlineStr">
@@ -1464,15 +1380,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="G18:J18"/>
-    <mergeCell ref="AB1:AE1"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="G16:J16"/>
-    <mergeCell ref="X1:AA1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="AF1:AI1"/>
     <mergeCell ref="O1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Сервер под московский узел проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
@@ -808,28 +808,62 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера. Четыре площадки уже имеют свои машины, новый сервер нужен только под Москву. Ставрополь (74 абонента) остаётся на ростовском сервере, как сейчас.</t>
+          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях. ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера; Ставрополь (74 абонента) остаётся на ростовском, как сейчас.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Резервный мастер отдельной машиной</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Пятый сервер занят московским узлом. Отдельная машина под тёплый резерв не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел. Процедура отрабатывается на этапе 7 учебно.</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел; процедура отрабатывается на этапе 7 учебно. На своих ВМ выделенный резерв возможен, но требует ДВУХ машин: шестой узел делает число чётным, и кворум приходится добирать арбитром garbd. Это правка одного этапа.</t>
         </is>
       </c>
     </row>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -89,7 +89,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,11 +153,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,7 +173,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,26 +188,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -566,18 +575,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="96" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Отказоустойчивый кластер телефонии на шесть регионов</t>
+          <t>Централизованная телефония на Asterisk с выносами в кластерах</t>
         </is>
       </c>
     </row>
@@ -608,322 +617,473 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>ОСНОВАНИЕ</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>протокол совещания, п. 3</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Скорректированная архитектура</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Савенко В. — до 05.08, выполнено</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Из протокола, п. 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>План работ</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Цеховской В. — срок 20.08</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Из протокола, п. 3. Настоящий файл и есть этот план.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>централизованная, с выносами</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Центральный узел — Ростов: мастер базы, FreePBX, управление. Выносы — Нижний Новгород, Славянск-на-Кубани, Москва, Воронеж — работают узлами одного кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят на центральный узел.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Дата начала работ</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>46272</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 13 недель не входят и идут до них.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Длительность, недель</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>План внедрения, docs/12-rollout-schedule.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Дата завершения работ</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Дата начала + 13 недель, последний рабочий день</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Сумма по этапам, см. лист плана</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Этапы 1–7. Помещается в 13 недель × 5 дней = 65 ч-д одного человека.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Этапы 8–9 (консолидация мелких АТС и перенумерация) — работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером 85 ч-д за 13 недель не выполняются, это ограничение плана, а не оценка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>11515</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+      <c r="B11" s="6" t="n">
+        <v>46374</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <f>B8*B11</f>
-        <v>978775</v>
+          <t>ЭТАП 1 — все, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–11, 810 абонентов</t>
+        </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>ЭТАП 2 — Воронеж</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>недели 12–15, 445 абонентов</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Пилотная площадка</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Из оставшихся Нижний Новгород — самый крупный (164) и единственный со своей станцией и станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком. Москва проще: её абоненты уже в базе центрального узла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Сумма по задачам, см. лист плана</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>11515</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>B15*B18</f>
+        <v>1024835</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Абонентов в периметре</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>1255</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Станций сейчас</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Там же</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Узлов кластера после внедрения</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Ростов (мастер) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Ростов (центральный) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Голосов в кворуме</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Пять узлов, число нечётное — отдельный арбитр не нужен. Кластер переживает потерю двух узлов из пяти.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>ВНИМАНИЕ. Пока Воронеж не введён, узлов четыре — число чётное. Кластер переживает потерю только одного узла, а при разрыве сети пополам ни одна половина не имеет большинства. Это состояние держится недели 8–11; если оно нежелательно, на этот период ставится арбитр garbd (1 vCPU, 512 МБ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Серверов нужно докупить</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях. ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера; Ставрополь (74 абонента) остаётся на ростовском, как сейчас.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Размещение ВМ по хостам</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>проверить</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Снимки ВМ как резервная копия</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>нельзя</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Резервный мастер отдельной машиной</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Резервный центральный узел отдельной машиной</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел; процедура отрабатывается на этапе 7 учебно. На своих ВМ выделенный резерв возможен, но требует ДВУХ машин: шестой узел делает число чётным, и кворум приходится добирать арбитром garbd. Это правка одного этапа.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Не требуется: каждый вынос — клон центрального узла, FreePBX на нём уже установлен и только отключён, поэтому роль передаётся на любой рабочий вынос; процедура отрабатывается в задаче 7 учебно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за стадии. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -940,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:W18"/>
+  <dimension ref="C1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.699999999999999" customWidth="1" min="1" max="1"/>
@@ -966,460 +1126,549 @@
     <col width="3.9" customWidth="1" min="21" max="21"/>
     <col width="3.9" customWidth="1" min="22" max="22"/>
     <col width="3.9" customWidth="1" min="23" max="23"/>
+    <col width="3.9" customWidth="1" min="24" max="24"/>
+    <col width="3.9" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Статус проекта</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Срок проекта</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Проект</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Стадии выполнения работ</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>ТРЗ, ч/д</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Проблемы/Риски</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>Сентябрь 2026</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>Октябрь 2026</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
         <is>
           <t>Ноябрь 2026</t>
         </is>
       </c>
+      <c r="X1" s="14" t="inlineStr">
+        <is>
+          <t>Декабрь 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>07-13</t>
         </is>
       </c>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="L2" s="15" t="inlineStr">
         <is>
           <t>14-20</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>21-27</t>
         </is>
       </c>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>28-04</t>
         </is>
       </c>
-      <c r="O2" s="13" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>05-11</t>
         </is>
       </c>
-      <c r="P2" s="13" t="inlineStr">
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>12-18</t>
         </is>
       </c>
-      <c r="Q2" s="13" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>19-25</t>
         </is>
       </c>
-      <c r="R2" s="13" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>26-01</t>
         </is>
       </c>
-      <c r="S2" s="13" t="inlineStr">
+      <c r="S2" s="15" t="inlineStr">
         <is>
           <t>02-08</t>
         </is>
       </c>
-      <c r="T2" s="13" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>09-15</t>
         </is>
       </c>
-      <c r="U2" s="13" t="inlineStr">
+      <c r="U2" s="15" t="inlineStr">
         <is>
           <t>16-22</t>
         </is>
       </c>
-      <c r="V2" s="13" t="inlineStr">
+      <c r="V2" s="15" t="inlineStr">
         <is>
           <t>23-29</t>
         </is>
       </c>
-      <c r="W2" s="13" t="inlineStr">
+      <c r="W2" s="15" t="inlineStr">
         <is>
           <t>30-06</t>
         </is>
       </c>
+      <c r="X2" s="15" t="inlineStr">
+        <is>
+          <t>07-13</t>
+        </is>
+      </c>
+      <c r="Y2" s="15" t="inlineStr">
+        <is>
+          <t>14-20</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>норма</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>07.09.26 - 04.12.26</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>07.09.26 - 18.12.26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Отказоустойчивый кластер телефонии на шесть регионов</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="14">
-        <f>SUM(I4:I12)</f>
-        <v>85</v>
-      </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="H3" s="17" t="n"/>
+      <c r="I3" s="16">
+        <f>SUM(I4:I15)</f>
+        <v>89</v>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>1255 абонентов на 12 станциях сводятся в кластер из 8 узлов. Два узла (Ставрополь, Москва) создаются заново — своей АТС там нет, абоненты обслуживаются из Ростова. Контрольная точка после первой площадки: тиражирование не начинается, пока Воронеж не отработает две недели без замечаний.</t>
         </is>
       </c>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="16" t="n"/>
-      <c r="M3" s="16" t="n"/>
-      <c r="N3" s="16" t="n"/>
-      <c r="O3" s="16" t="n"/>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
-      <c r="R3" s="16" t="n"/>
-      <c r="S3" s="16" t="n"/>
-      <c r="T3" s="16" t="n"/>
-      <c r="U3" s="16" t="n"/>
-      <c r="V3" s="16" t="n"/>
-      <c r="W3" s="16" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="18" t="n"/>
+      <c r="M3" s="18" t="n"/>
+      <c r="N3" s="18" t="n"/>
+      <c r="O3" s="18" t="n"/>
+      <c r="P3" s="18" t="n"/>
+      <c r="Q3" s="18" t="n"/>
+      <c r="R3" s="18" t="n"/>
+      <c r="S3" s="18" t="n"/>
+      <c r="T3" s="18" t="n"/>
+      <c r="U3" s="18" t="n"/>
+      <c r="V3" s="18" t="n"/>
+      <c r="W3" s="18" t="n"/>
+      <c r="X3" s="18" t="n"/>
+      <c r="Y3" s="18" t="n"/>
     </row>
     <row r="4">
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>1. Подготовка: сеть, серверы, договорённости с операторами</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1. Подготовка: сеть, виртуальные машины, договорённости с операторами</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n"/>
-      <c r="I4" s="17" t="n">
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t>RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию, получает автономную АТС с транком. Отсутствие IP у Славянска-на-Кубани и локального PBX блокирует недели 8 и 12. Оператор может не дать отдельных пользователей ВАТС — тогда площадка работает через мастер.</t>
-        </is>
-      </c>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="16" t="n"/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию, получает автономную АТС с транком. Отсутствие IP у Славянска-на-Кубани и локального PBX блокирует недели 7 и 10. Оператор может не дать отдельных пользователей ВАТС — тогда вынос работает через центральный узел.</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>2. Смена учётных данных и защита периметра</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="17" t="n">
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="17" t="inlineStr"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="16" t="n"/>
+      <c r="J5" s="19" t="inlineStr"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>3. Испытательный стенд</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="17" t="n">
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="M6" s="16" t="n"/>
+      <c r="J6" s="19" t="inlineStr"/>
+      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>4. Перевод ростовской АТС в режим мастера кластера</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>4. Ростов — центральный узел кластера</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H7" s="18" t="n"/>
-      <c r="I7" s="17" t="n">
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Требуется окно на перезапуск базы: новые вызовы не устанавливаются около минуты.</t>
         </is>
       </c>
-      <c r="N7" s="16" t="n"/>
+      <c r="N7" s="18" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>5. Первая площадка — Воронеж</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>5. Пилотный вынос — Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="17" t="n">
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>Контрольная точка: при проблемах на Воронеже тиражирование не начинается, пока они не закрыты. При сжатом сроке это единственный запас в плане — сдвиг здесь двигает весь график.</t>
-        </is>
-      </c>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="16" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>Контрольная точка этапа 1. Пилот перенесён с Воронежа на Нижний Новгород: 445 абонентов Воронежа выведены во второй этап, поэтому обкатка идёт на 164 абонентах. Схема проверяется на меньшем масштабе, чем самая нагруженная площадка.</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="n"/>
+      <c r="P8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>6. Тиражирование на три площадки</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>6. Тиражирование на остальные выносы этапа 1</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H9" s="18" t="n"/>
-      <c r="I9" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>Узлы перевводятся по одному, работы по площадкам не совмещаются. Регион 5 в исходных данных назван «Москва, СПб, Новосибирск» — при реальном размещении абонентов в Новосибирске площадка исключается из синхронной репликации.</t>
-        </is>
-      </c>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
-      <c r="S9" s="16" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>Выносы вводятся по одному, работы по площадкам не совмещаются. Регион 5 в исходных данных назван «Москва, СПб, Новосибирск» — при реальном размещении абонентов в Новосибирске площадка исключается из синхронной репликации.</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>7. Учебная передача роли мастера</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>7. Учебная передача роли центрального узла</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="17" t="n">
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>Отдельной машины под резервный мастер нет: роль передаётся на один из рабочих узлов. Процедура обязана быть опробована заранее, иначе в аварию не сработает.</t>
-        </is>
-      </c>
-      <c r="T10" s="16" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>Отдельной машины под резервный центральный узел нет: роль передаётся на один из рабочих выносов. Процедура обязана быть опробована заранее.</t>
+        </is>
+      </c>
+      <c r="S10" s="18" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>8. Консолидация мелких АТС</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>8. Консолидация мелких АТС этапа 1</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" s="17" t="inlineStr"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="16" t="n"/>
-      <c r="S11" s="16" t="n"/>
-      <c r="T11" s="16" t="n"/>
-      <c r="U11" s="16" t="n"/>
-      <c r="V11" s="16" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="18" t="n"/>
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>9. Перевод абонентов на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>9. Перевод абонентов этапа 1 на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="H12" s="18" t="n"/>
-      <c r="I12" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>Организационный поток, идёт силами второго исполнителя. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
         </is>
       </c>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-      <c r="S12" s="16" t="n"/>
-      <c r="T12" s="16" t="n"/>
-      <c r="U12" s="16" t="n"/>
-      <c r="V12" s="16" t="n"/>
-      <c r="W12" s="16" t="n"/>
+      <c r="O12" s="18" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="n"/>
+      <c r="U12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>10. Воронежский вынос</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>САМЫЙ КРУПНЫЙ ВЫНОС ИДЁТ ПОСЛЕДНИМ. Плюс: к неделе 12 процедура отработана на трёх площадках. Минус: 445 абонентов — треть периметра — переводятся в конце графика, и запаса после них не остаётся. Резерв на этап 2 не заложен; если он нужен, срок сдвигается вправо, а не ужимается.</t>
+        </is>
+      </c>
+      <c r="V13" s="18" t="n"/>
+      <c r="W13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>11. Консолидация воронежских АТС</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>Мясокомбинат — 187 абонентов, вторая по величине станция периметра. Переносится сразу после ввода воронежского выноса, в ту же неделю не совмещать.</t>
+        </is>
+      </c>
+      <c r="W14" s="18" t="n"/>
+      <c r="X14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="F15" s="7" t="inlineStr">
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>12. Перевод воронежских абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" s="19" t="inlineStr"/>
+      <c r="W15" s="18" t="n"/>
+      <c r="X15" s="18" t="n"/>
+      <c r="Y15" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Статусы открытых/закрытых проектов:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="F16" s="19" t="inlineStr">
+    <row r="19">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>норма</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>отклонений по плановым срокам основных вех/трудозатратам нет</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="F17" s="20" t="inlineStr">
+    <row r="20">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>внимание</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>есть вероятность отклонений по плановым срокам основных вех/трудозатратам, которые могут повлиять на изменение плановых сроков/трудозатрат проекта</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="F18" s="21" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>тревога</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>есть отклонения по плановым срокам основных вех/трудозатратам</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G17:J17"/>
+  <mergeCells count="7">
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="S1:W1"/>
-    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G21:J21"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="G19:J19"/>
     <mergeCell ref="O1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Централизованная телефония на Asterisk с выносами в кластерах</t>
+          <t>Централизованная телефония на Asterisk: центр в московском ЦОД, выносы по городам</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.»</t>
+          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД — мастер на первой площадке, копия на второй; остальные узлы по городам.</t>
         </is>
       </c>
     </row>
@@ -673,417 +673,502 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>централизованная, с выносами</t>
+          <t>центр в ЦОД + выносы</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центральный узел — Ростов: мастер базы, FreePBX, управление. Выносы — Нижний Новгород, Славянск-на-Кубани, Москва, Воронеж — работают узлами одного кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят на центральный узел.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>46272</v>
+          <t>Два зала ЦОД — независимы?</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ ДО СТАРТА</t>
+        </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>КРИТИЧНО. Копия во втором зале даёт резервирование только если залы не делят физический хост, ввод питания и аплинк. Две стойки одного зала за одним вводом — это не две площадки, и вся схема резервирования теряет смысл. Проверяется в задаче 1 до выделения ВМ.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>15</v>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Дата завершения работ</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>46374</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Дата начала + 15 недель, последний рабочий день</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 1 — все, кроме Воронежа</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>недели 1–11, 810 абонентов</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 (Москва) 80, ЦОД-2 копия, Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>недели 12–15, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>недели 13–16, 445 абонентов</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Пилотная площадка</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Из оставшихся Нижний Новгород — самый крупный (164) и единственный со своей станцией и станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком. Москва проще: её абоненты уже в базе центрального узла.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>89</v>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 426 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>59</v>
+          <t>Пилотный вынос</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>11515</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B19" s="7">
-        <f>B15*B18</f>
-        <v>1024835</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>11515</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>B17*B20</f>
+        <v>1093925</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>5</v>
+        <v>1255</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Ростов (центральный) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Пять узлов, число нечётное — отдельный арбитр не нужен. Кластер переживает потерю двух узлов из пяти.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Пока Воронеж не введён, узлов четыре — число чётное. Кластер переживает потерю только одного узла, а при разрыве сети пополам ни одна половина не имеет большинства. Это состояние держится недели 8–11; если оно нежелательно, на этот период ставится арбитр garbd (1 vCPU, 512 МБ).</t>
+          <t>ЦОД-1 40, ЦОД-2 40 (оба живые), Ростов 426, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Абонентов 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Серверов нужно докупить</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях.</t>
+          <t>Шесть узлов — число ЧЁТНОЕ, поэтому нужен арбитр garbd: он даёт седьмой голос и не хранит данные. Кластер переживает потерю двух узлов и остаётся работоспособным при потере ЦОД целиком (четыре голоса из семи в городах).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Где стоит арбитр</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>Ростов, отдельная ВМ</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>НЕ в ЦОД. Если поставить арбитр в ЦОД, потеря дата-центра уносит три голоса из семи разом. В Ростове — самая крупная площадка после Воронежа и своя инфраструктура. Требования: 1 vCPU, 512 МБ.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>Пять узлов — нечётное, арбитр на этапе 1 не нужен. Он ставится в задаче 11 вместе с вводом Воронежа, который делает число узлов чётным.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Резервный центральный узел отдельной машиной</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Не требуется: каждый вынос — клон центрального узла, FreePBX на нём уже установлен и только отключён, поэтому роль передаётся на любой рабочий вынос; процедура отрабатывается в задаче 7 учебно.</t>
+          <t>ЦОД-1, ЦОД-2 и ВМ под арбитр в Ростове. Все — свои мощности, закупки нет. У четырёх городских площадок машины уже есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Неделя 16 — предновогодняя</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>21–25 декабря</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Дата протокола совещания</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1100,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:Y21"/>
+  <dimension ref="C1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.699999999999999" customWidth="1" min="1" max="1"/>
@@ -1128,6 +1213,7 @@
     <col width="3.9" customWidth="1" min="23" max="23"/>
     <col width="3.9" customWidth="1" min="24" max="24"/>
     <col width="3.9" customWidth="1" min="25" max="25"/>
+    <col width="3.9" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1268,6 +1354,11 @@
           <t>14-20</t>
         </is>
       </c>
+      <c r="Z2" s="15" t="inlineStr">
+        <is>
+          <t>21-27</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="C3" s="16" t="inlineStr">
@@ -1277,7 +1368,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>07.09.26 - 18.12.26</t>
+          <t>07.09.26 - 25.12.26</t>
         </is>
       </c>
       <c r="E3" s="17" t="n"/>
@@ -1293,8 +1384,8 @@
       </c>
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="16">
-        <f>SUM(I4:I15)</f>
-        <v>89</v>
+        <f>SUM(I4:I16)</f>
+        <v>95</v>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
@@ -1316,6 +1407,7 @@
       <c r="W3" s="18" t="n"/>
       <c r="X3" s="18" t="n"/>
       <c r="Y3" s="18" t="n"/>
+      <c r="Z3" s="18" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="19" t="n"/>
@@ -1323,7 +1415,7 @@
       <c r="E4" s="19" t="n"/>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>1. Подготовка: сеть, виртуальные машины, договорённости с операторами</t>
+          <t>1. Подготовка: ЦОД, сеть, виртуальные машины, договорённости с операторами</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -1337,7 +1429,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию, получает автономную АТС с транком. Отсутствие IP у Славянска-на-Кубани и локального PBX блокирует недели 7 и 10. Оператор может не дать отдельных пользователей ВАТС — тогда вынос работает через центральный узел.</t>
+          <t>КЛЮЧЕВАЯ ПРОВЕРКА: два зала ЦОД обязаны быть независимы по хосту, питанию и аплинку. Если это две стойки одного зала за одним вводом, копия во втором зале не даёт резервирования и вся схема теряет смысл. Также: RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию.</t>
         </is>
       </c>
       <c r="K4" s="18" t="n"/>
@@ -1392,7 +1484,7 @@
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>4. Ростов — центральный узел кластера</t>
+          <t>4. Ростовская АТС — первый узел кластера</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -1417,7 +1509,7 @@
       <c r="E8" s="19" t="n"/>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>5. Пилотный вынос — Нижний Новгород</t>
+          <t>5. Центр в московском ЦОД: два живых узла в разных залах</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1431,7 +1523,7 @@
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>Контрольная точка этапа 1. Пилот перенесён с Воронежа на Нижний Новгород: 445 абонентов Воронежа выведены во второй этап, поэтому обкатка идёт на 164 абонентах. Схема проверяется на меньшем масштабе, чем самая нагруженная площадка.</t>
+          <t>Перенос центра из Ростова в ЦОД — самая ответственная операция этапа 1. Передача роли мастера здесь боевая, а не учебная, поэтому процедура обязана быть отработана на стенде (задача 3). Откат: роль возвращается на Ростов, который остаётся полноценным узлом.</t>
         </is>
       </c>
       <c r="O8" s="18" t="n"/>
@@ -1443,7 +1535,7 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>6. Тиражирование на остальные выносы этапа 1</t>
+          <t>6. Пилотный вынос — Нижний Новгород</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1457,7 +1549,7 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>Выносы вводятся по одному, работы по площадкам не совмещаются. Регион 5 в исходных данных назван «Москва, СПб, Новосибирск» — при реальном размещении абонентов в Новосибирске площадка исключается из синхронной репликации.</t>
+          <t>Контрольная точка этапа 1. Пилот — Нижний Новгород: Воронеж по решению совещания вынесен во второй этап и пилотом быть не может.</t>
         </is>
       </c>
       <c r="Q9" s="18" t="n"/>
@@ -1469,7 +1561,7 @@
       <c r="E10" s="19" t="n"/>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>7. Учебная передача роли центрального узла</t>
+          <t>7. Вынос Славянск-на-Кубани</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1479,13 +1571,9 @@
       </c>
       <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>Отдельной машины под резервный центральный узел нет: роль передаётся на один из рабочих выносов. Процедура обязана быть опробована заранее.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J10" s="19" t="inlineStr"/>
       <c r="S10" s="18" t="n"/>
     </row>
     <row r="11">
@@ -1494,7 +1582,7 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>8. Консолидация мелких АТС этапа 1</t>
+          <t>8. Учебное переключение управления между залами ЦОД</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1504,12 +1592,13 @@
       </c>
       <c r="H11" s="20" t="n"/>
       <c r="I11" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="19" t="inlineStr"/>
-      <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="18" t="n"/>
-      <c r="S11" s="18" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>Панель FreePBX обязана быть включена РОВНО на одном узле: две активные панели пишут в общую базу наперегонки. Вызовы это не затрагивает — их несут оба зала постоянно. Время переключения измеряется и вносится в регламент.</t>
+        </is>
+      </c>
       <c r="T11" s="18" t="n"/>
     </row>
     <row r="12">
@@ -1518,7 +1607,7 @@
       <c r="E12" s="19" t="n"/>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>9. Перевод абонентов этапа 1 на единый план нумерации</t>
+          <t>9. Консолидация мелких АТС этапа 1</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
@@ -1528,16 +1617,9 @@
       </c>
       <c r="H12" s="20" t="n"/>
       <c r="I12" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>Организационный поток, идёт силами второго исполнителя. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
-        </is>
-      </c>
-      <c r="O12" s="18" t="n"/>
-      <c r="P12" s="18" t="n"/>
-      <c r="Q12" s="18" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="J12" s="19" t="inlineStr"/>
       <c r="R12" s="18" t="n"/>
       <c r="S12" s="18" t="n"/>
       <c r="T12" s="18" t="n"/>
@@ -1549,7 +1631,7 @@
       <c r="E13" s="19" t="n"/>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>10. Воронежский вынос</t>
+          <t>10. Перевод абонентов этапа 1 на единый план нумерации</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -1559,15 +1641,20 @@
       </c>
       <c r="H13" s="20" t="n"/>
       <c r="I13" s="19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>САМЫЙ КРУПНЫЙ ВЫНОС ИДЁТ ПОСЛЕДНИМ. Плюс: к неделе 12 процедура отработана на трёх площадках. Минус: 445 абонентов — треть периметра — переводятся в конце графика, и запаса после них не остаётся. Резерв на этап 2 не заложен; если он нужен, срок сдвигается вправо, а не ужимается.</t>
-        </is>
-      </c>
+          <t>Организационный поток, идёт силами второго исполнителя. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="18" t="n"/>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="18" t="n"/>
+      <c r="U13" s="18" t="n"/>
       <c r="V13" s="18" t="n"/>
-      <c r="W13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="19" t="n"/>
@@ -1575,7 +1662,7 @@
       <c r="E14" s="19" t="n"/>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>11. Консолидация воронежских АТС</t>
+          <t>11. Воронежский вынос и арбитр кворума</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -1585,11 +1672,11 @@
       </c>
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>Мясокомбинат — 187 абонентов, вторая по величине станция периметра. Переносится сразу после ввода воронежского выноса, в ту же неделю не совмещать.</t>
+          <t>С вводом Воронежа узлов шесть — ЧЁТНОЕ ЧИСЛО. Без арбитра при разрыве сети пополам большинства нет ни у одной половины. Арбитр ставится в Ростове, а не в ЦОД: иначе потеря ЦОД целиком уносит три голоса из семи. Кроме того, 445 абонентов — треть периметра — переводятся в конце графика, запаса после них не остаётся.</t>
         </is>
       </c>
       <c r="W14" s="18" t="n"/>
@@ -1601,7 +1688,7 @@
       <c r="E15" s="19" t="n"/>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>12. Перевод воронежских абонентов на единый план нумерации</t>
+          <t>12. Консолидация воронежских АТС</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -1614,48 +1701,74 @@
         <v>6</v>
       </c>
       <c r="J15" s="19" t="inlineStr"/>
-      <c r="W15" s="18" t="n"/>
       <c r="X15" s="18" t="n"/>
       <c r="Y15" s="18" t="n"/>
     </row>
-    <row r="18">
-      <c r="F18" s="8" t="inlineStr">
+    <row r="16">
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>13. Перевод воронежских абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>Неделя 16 приходится на предновогоднюю — 21–25 декабря. Перевод номеров в эту неделю нежелателен: люди в отпусках, изменения некому проверять. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
+        </is>
+      </c>
+      <c r="X16" s="18" t="n"/>
+      <c r="Y16" s="18" t="n"/>
+      <c r="Z16" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Статусы открытых/закрытых проектов:</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="F19" s="21" t="inlineStr">
+    <row r="20">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>норма</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>отклонений по плановым срокам основных вех/трудозатратам нет</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="22" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>внимание</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>есть вероятность отклонений по плановым срокам основных вех/трудозатратам, которые могут повлиять на изменение плановых сроков/трудозатрат проекта</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="F21" s="23" t="inlineStr">
+    <row r="22">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>тревога</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>есть отклонения по плановым срокам основных вех/трудозатратам</t>
         </is>
@@ -1663,13 +1776,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="O1:R1"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -678,497 +678,548 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Два зала ЦОД — независимы?</t>
+          <t>Стойки в ЦОД — независимы</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ПРОВЕРИТЬ ДО СТАРТА</t>
+          <t>ПОДТВЕРЖДЕНО</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Копия во втором зале даёт резервирование только если залы не делят физический хост, ввод питания и аплинк. Две стойки одного зала за одним вводом — это не две площадки, и вся схема резервирования теряет смысл. Проверяется в задаче 1 до выделения ВМ.</t>
+          <t>Стойки свои, независимость подтверждена заказчиком. Это снимает главный риск схемы: два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>46272</v>
+          <t>SIP-пользователи у операторов</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>заводим сами</t>
+        </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Доступ к кабинету ВАТС есть, учётные записи на площадки создаются самостоятельно. Внешнего согласования и ожидания оператора нет.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>16</v>
+          <t>Внешних зависимостей</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>Все площадки свои, адреса известны, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, ПО бесплатное, машины на своей виртуализации. Сроки зависят только от собственных ресурсов — это редкая ситуация, и она означает, что сдвиг графика будет внутренней причиной, а не внешней.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>Дата завершения работ</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B14" s="6" t="n">
         <v>46381</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>недели 1–12, 810 абонентов</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>ЦОД-1 (Москва) 80, ЦОД-2 копия, Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>недели 13–16, 445 абонентов</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Порядок переноса центра</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 426 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>95</v>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>65</v>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>30</v>
+          <t>Пилотный вынос</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11515</v>
+        <v>98</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B21" s="7">
-        <f>B17*B20</f>
-        <v>1093925</v>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1255</v>
+        <v>11515</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>B20*B23</f>
+        <v>1128470</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>6</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40, ЦОД-2 40 (оба живые), Ростов 426, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Абонентов 1255 — сходится с аудитом.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>1255</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Шесть узлов — число ЧЁТНОЕ, поэтому нужен арбитр garbd: он даёт седьмой голос и не хранит данные. Кластер переживает потерю двух узлов и остаётся работоспособным при потере ЦОД целиком (четыре голоса из семи в городах).</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Где стоит арбитр</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Ростов, отдельная ВМ</t>
-        </is>
+          <t>Станций сейчас</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>НЕ в ЦОД. Если поставить арбитр в ЦОД, потеря дата-центра уносит три голоса из семи разом. В Ростове — самая крупная площадка после Воронежа и своя инфраструктура. Требования: 1 vCPU, 512 МБ.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Пять узлов — нечётное, арбитр на этапе 1 не нужен. Он ставится в задаче 11 вместе с вводом Воронежа, который делает число узлов чётным.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и ВМ под арбитр в Ростове. Все — свои мощности, закупки нет. У четырёх городских площадок машины уже есть.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Арбитр garbd</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>не нужен</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Размещение ВМ по хостам</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>проверить</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Номер приказа / внутреннего проекта</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Номер приказа / внутреннего проекта</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1385,7 +1436,7 @@
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="16">
         <f>SUM(I4:I16)</f>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
@@ -1429,7 +1480,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>КЛЮЧЕВАЯ ПРОВЕРКА: два зала ЦОД обязаны быть независимы по хосту, питанию и аплинку. Если это две стойки одного зала за одним вводом, копия во втором зале не даёт резервирования и вся схема теряет смысл. Также: RTT выше 50 мс до площадки — площадка не включается в синхронную репликацию.</t>
+          <t>Внешних зависимостей у проекта нет: площадки свои, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, адреса известны. Единственный оставшийся риск этой задачи — RTT: выше 50 мс до площадки означает, что она не включается в синхронную репликацию и получает автономную АТС с транком. Всё остальное зависит только от собственных сроков.</t>
         </is>
       </c>
       <c r="K4" s="18" t="n"/>
@@ -1549,7 +1600,7 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>Контрольная точка этапа 1. Пилот — Нижний Новгород: Воронеж по решению совещания вынесен во второй этап и пилотом быть не может.</t>
+          <t>Контрольная точка этапа 1. Пилот — Нижний Новгород: Воронеж по решению совещания вынесен во второй этап и пилотом быть не может, а Ростов к этому моменту уже узел.</t>
         </is>
       </c>
       <c r="Q9" s="18" t="n"/>
@@ -1561,7 +1612,7 @@
       <c r="E10" s="19" t="n"/>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>7. Вынос Славянск-на-Кубани</t>
+          <t>7. Учебное переключение управления между залами ЦОД</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1571,9 +1622,13 @@
       </c>
       <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>Панель FreePBX обязана быть включена РОВНО на одном узле: две активные панели пишут в общую базу наперегонки. Вызовы это не затрагивает — их несут оба зала постоянно.</t>
+        </is>
+      </c>
       <c r="S10" s="18" t="n"/>
     </row>
     <row r="11">
@@ -1582,7 +1637,7 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>8. Учебное переключение управления между залами ЦОД</t>
+          <t>8. Выносы Славянск-на-Кубани и Ставрополь</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1592,14 +1647,15 @@
       </c>
       <c r="H11" s="20" t="n"/>
       <c r="I11" s="19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>Панель FreePBX обязана быть включена РОВНО на одном узле: две активные панели пишут в общую базу наперегонки. Вызовы это не затрагивает — их несут оба зала постоянно. Время переключения измеряется и вносится в регламент.</t>
+          <t>На неделях 11–12 узлов шесть — число чётное: кластер переживает потерю только двух узлов, а при разрыве сети пополам большинства нет ни у одной половины. Окно короткое и закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
       <c r="T11" s="18" t="n"/>
+      <c r="U11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="19" t="n"/>
@@ -1662,7 +1718,7 @@
       <c r="E14" s="19" t="n"/>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>11. Воронежский вынос и арбитр кворума</t>
+          <t>11. Воронежский вынос</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -1672,11 +1728,11 @@
       </c>
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>С вводом Воронежа узлов шесть — ЧЁТНОЕ ЧИСЛО. Без арбитра при разрыве сети пополам большинства нет ни у одной половины. Арбитр ставится в Ростове, а не в ЦОД: иначе потеря ЦОД целиком уносит три голоса из семи. Кроме того, 445 абонентов — треть периметра — переводятся в конце графика, запаса после них не остаётся.</t>
+          <t>445 абонентов — треть периметра — переводятся в конце графика, запаса после них не остаётся. Зато с вводом Воронежа узлов становится семь: число нечётное, арбитр в итоговой схеме не нужен.</t>
         </is>
       </c>
       <c r="W14" s="18" t="n"/>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -685,309 +685,307 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Стойки в ЦОД — независимы</t>
+          <t>Стойки в ЦОД</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО</t>
+          <t>наши, залы независимы</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Стойки свои, независимость подтверждена заказчиком. Это снимает главный риск схемы: два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания.</t>
+          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SIP-пользователи у операторов</t>
+          <t>Ждать никого не нужно</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>заводим сами</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Доступ к кабинету ВАТС есть, учётные записи на площадки создаются самостоятельно. Внешнего согласования и ожидания оператора нет.</t>
+          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Внешних зависимостей</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Все площадки свои, адреса известны, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, ПО бесплатное, машины на своей виртуализации. Сроки зависят только от собственных ресурсов — это редкая ситуация, и она означает, что сдвиг графика будет внутренней причиной, а не внешней.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>46272</v>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>16</v>
+          <t>Дата завершения работ</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>46381</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Дата завершения работ</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>46381</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Дата начала + 15 недель, последний рабочий день</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+          <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>недели 1–12, 810 абонентов</t>
+          <t>недели 13–16, 445 абонентов</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 2 — Воронеж</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>недели 13–16, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Ставрополь получает свою АТС</t>
+          <t>Порядок переноса центра</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>да, задача 8.2</t>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Порядок переноса центра</t>
+          <t>Пилотный вынос</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30</v>
+        <v>11515</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>11515</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>B19*B22</f>
+        <v>1128470</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>B20*B23</f>
-        <v>1128470</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>0</v>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1255</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -995,231 +993,216 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>7</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Виртуальных машин добавить</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>3</v>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Снимки ВМ как резервная копия</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>нельзя</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Оба узла ЦОД — живые</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Панель управления FreePBX</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>ровно на одном узле</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>21–25 декабря</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Неделя 16 — предновогодняя</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>21–25 декабря</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Что нужно заполнить вручную</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Что нужно заполнить вручную</t>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Дата протокола совещания</t>
         </is>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
+          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Адресный план узлов</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>Адресный план узлов</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1480,7 +1463,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>Внешних зависимостей у проекта нет: площадки свои, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, адреса известны. Единственный оставшийся риск этой задачи — RTT: выше 50 мс до площадки означает, что она не включается в синхронную репликацию и получает автономную АТС с транком. Всё остальное зависит только от собственных сроков.</t>
+          <t>Единственная точка принятия решения во всём плане — RTT: выше 50 мс до площадки означает, что мы не включаем её в синхронную репликацию и ставим автономную АТС с транком до ЦОД. Всё остальное в этой задаче делаем сами и в своём темпе: ждать нам никого не нужно.</t>
         </is>
       </c>
       <c r="K4" s="18" t="n"/>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -627,582 +627,548 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД — мастер на первой площадке, копия на второй; остальные узлы по городам.</t>
+          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД, на обеих площадках живые узлы; остальные узлы по городам.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Скорректированная архитектура</t>
+          <t>Архитектура</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Савенко В. — до 05.08, выполнено</t>
+          <t>центр в ЦОД + выносы</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Из протокола, п. 3.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>План работ</t>
+          <t>Стойки в ЦОД</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Цеховской В. — срок 20.08</t>
+          <t>наши, залы независимы</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Из протокола, п. 3. Настоящий файл и есть этот план.</t>
+          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Архитектура</t>
+          <t>Ждать никого не нужно</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>центр в ЦОД + выносы</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
+          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Стойки в ЦОД</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>наши, залы независимы</t>
-        </is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ждать никого не нужно</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
+          <t>Дата завершения работ</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46272</v>
+        <v>46381</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Дата завершения работ</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>46381</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Дата начала + 15 недель, последний рабочий день</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 2 — Воронеж</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>недели 13–16, 445 абонентов</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>недели 1–12, 810 абонентов</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 2 — Воронеж</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>недели 13–16, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ставрополь получает свою АТС</t>
+          <t>Пилотный вынос</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>да, задача 8.2</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Порядок переноса центра</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
-        </is>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>68</v>
+        <v>11515</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>30</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>B17*B20</f>
+        <v>1128470</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>11515</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>B19*B22</f>
-        <v>1128470</v>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
+          <t>Станций сейчас</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1255</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>7</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Кворум в конце этапа 1</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>6</v>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>3</v>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Оба узла ЦОД — живые</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Панель управления FreePBX</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>ровно на одном узле</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>21–25 декабря</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Панель управления FreePBX</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>ровно на одном узле</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Неделя 16 — предновогодняя</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>21–25 декабря</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Что нужно заполнить вручную</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Что нужно заполнить вручную</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Исполнитель</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Дата протокола совещания</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Адресный план узлов</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Дата протокола совещания</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Адресный план узлов</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -803,372 +803,406 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Ставрополь</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Порядок ввода выносов: Ставрополь (пилот), затем Нижний Новгород, затем Славянск-на-Кубани. ВАЖНО ПОНИМАТЬ: у Ставрополя нет своей станции — его 74 абонента уже в общей базе, поэтому пилот проверяет кластер, каналы и провижининг, но НЕ проверяет перенос действующей АТС с её гашением. Эта часть процедуры впервые отрабатывается на Нижнем Новгороде (задача 8.1) — её стоит пройти с тем же вниманием, что и пилот.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>98</v>
+          <t>Оповещение техподдержки</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>задача 1.7</t>
+        </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>До начала работ согласован порядок: кто и по какому каналу поднимается по тревоге, за какое время и что считается инцидентом. Порядок роздан всем участникам работ — иначе в первую же нештатную ситуацию искать будет некого.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>68</v>
+          <t>Исполнитель организационных задач</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Задачи 9, 10, 12, 13 — консолидация мелких АТС и перенумерация. Инженер кластера на задачи 1–8 и 11 в файле не проставлен: ячейки оставлены жёлтыми под заполнение.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11515</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B21" s="7">
-        <f>B17*B20</f>
-        <v>1128470</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>11515</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>B19*B22</f>
+        <v>1128470</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>7</v>
+        <v>1255</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Узлов кластера после внедрения</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>3</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Размещение ВМ по хостам</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>проверить</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Снимки ВМ как резервная копия</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>нельзя</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Адресный план узлов</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
+          <t>Присваивается при открытии проекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1374,7 +1408,7 @@
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Отказоустойчивый кластер телефонии на шесть регионов</t>
+          <t>Централизованная телефония на Asterisk: центр в ЦОД, семь узлов</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
@@ -1535,7 +1569,7 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>6. Пилотный вынос — Нижний Новгород</t>
+          <t>6. Пилотный вынос — Ставрополь</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1586,7 +1620,7 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>8. Выносы Славянск-на-Кубани и Ставрополь</t>
+          <t>8. Выносы Нижний Новгород и Славянск-на-Кубани</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">

--- a/docs/plan/dit-project-registry.xlsx
+++ b/docs/plan/dit-project-registry.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>задача 1.7</t>
+          <t>задача 3</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -830,379 +830,417 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Исполнитель организационных задач</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Кириевская Е.</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Задачи 9, 10, 12, 13 — консолидация мелких АТС и перенумерация. Инженер кластера на задачи 1–8 и 11 в файле не проставлен: ячейки оставлены жёлтыми под заполнение.</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>КОМАНДА ПРОЕКТА</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>четыре человека</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>98</v>
+          <t xml:space="preserve">  Руководитель</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Главный по проекту, указан заказчиком во всех строках плана.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>68</v>
+          <t xml:space="preserve">  Основной исполнитель</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Инженер кластера. Задачи 1–9 и 12 — вся работа с кластером, переносом центра и вводом выносов.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>30</v>
+          <t xml:space="preserve">  Помощник</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Задачи 10, 11, 13, 14 — консолидация мелких АТС и перенумерация. Частичная занятость, идут параллельно основным работам.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>11515</v>
+          <t xml:space="preserve">  Развёртывание и адресация</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Создание клонов, установка и присвоение IP-адресов на площадках. Проставлен исполнителем в соответствующих подзадачах.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>B19*B22</f>
-        <v>1128470</v>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1255</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>11515</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>7</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>B23*B26</f>
+        <v>1151500</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>7</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
+          <t>Голосов в кворуме</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Арбитр garbd</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>не нужен</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>ровно на одном узле</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Номер приказа / внутреннего проекта</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Присваивается при открытии проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Дата протокола совещания</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Адресный план узлов</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
+          <t>Присваивается при открытии проекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1219,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:Z22"/>
+  <dimension ref="C1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.699999999999999" customWidth="1" min="1" max="1"/>
@@ -1418,8 +1456,8 @@
       </c>
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="16">
-        <f>SUM(I4:I16)</f>
-        <v>98</v>
+        <f>SUM(I4:I17)</f>
+        <v>100</v>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
@@ -1497,7 +1535,7 @@
       <c r="E6" s="19" t="n"/>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>3. Испытательный стенд</t>
+          <t>3. Порядок оповещения техподдержки при отклонениях</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -1507,10 +1545,10 @@
       </c>
       <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6" s="19" t="inlineStr"/>
-      <c r="M6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="19" t="n"/>
@@ -1518,7 +1556,7 @@
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>4. Ростовская АТС — первый узел кластера</t>
+          <t>4. Испытательный стенд</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -1528,14 +1566,14 @@
       </c>
       <c r="H7" s="20" t="n"/>
       <c r="I7" s="19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Требуется окно на перезапуск базы: новые вызовы не устанавливаются около минуты.</t>
         </is>
       </c>
-      <c r="N7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="19" t="n"/>
@@ -1543,7 +1581,7 @@
       <c r="E8" s="19" t="n"/>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>5. Центр в московском ЦОД: два живых узла в разных залах</t>
+          <t>5. Ростовская АТС — первый узел кластера</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1553,15 +1591,14 @@
       </c>
       <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Перенос центра из Ростова в ЦОД — самая ответственная операция этапа 1. Передача роли мастера здесь боевая, а не учебная, поэтому процедура обязана быть отработана на стенде (задача 3). Откат: роль возвращается на Ростов, который остаётся полноценным узлом.</t>
         </is>
       </c>
-      <c r="O8" s="18" t="n"/>
-      <c r="P8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="19" t="n"/>
@@ -1569,7 +1606,7 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>6. Пилотный вынос — Ставрополь</t>
+          <t>6. Центр в московском ЦОД: два живых узла в разных залах</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1586,8 +1623,8 @@
           <t>Контрольная точка этапа 1. Пилот — Нижний Новгород: Воронеж по решению совещания вынесен во второй этап и пилотом быть не может, а Ростов к этому моменту уже узел.</t>
         </is>
       </c>
-      <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="19" t="n"/>
@@ -1595,7 +1632,7 @@
       <c r="E10" s="19" t="n"/>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>7. Учебное переключение управления между залами ЦОД</t>
+          <t>7. Пилотный вынос — Ставрополь</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1605,14 +1642,15 @@
       </c>
       <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Панель FreePBX обязана быть включена РОВНО на одном узле: две активные панели пишут в общую базу наперегонки. Вызовы это не затрагивает — их несут оба зала постоянно.</t>
         </is>
       </c>
-      <c r="S10" s="18" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="19" t="n"/>
@@ -1620,7 +1658,7 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>8. Выносы Нижний Новгород и Славянск-на-Кубани</t>
+          <t>8. Учебное переключение управления между залами ЦОД</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1630,15 +1668,14 @@
       </c>
       <c r="H11" s="20" t="n"/>
       <c r="I11" s="19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
           <t>На неделях 11–12 узлов шесть — число чётное: кластер переживает потерю только двух узлов, а при разрыве сети пополам большинства нет ни у одной половины. Окно короткое и закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
-      <c r="T11" s="18" t="n"/>
-      <c r="U11" s="18" t="n"/>
+      <c r="S11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="19" t="n"/>
@@ -1646,7 +1683,7 @@
       <c r="E12" s="19" t="n"/>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>9. Консолидация мелких АТС этапа 1</t>
+          <t>9. Выносы Нижний Новгород и Славянск-на-Кубани</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
@@ -1656,11 +1693,9 @@
       </c>
       <c r="H12" s="20" t="n"/>
       <c r="I12" s="19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J12" s="19" t="inlineStr"/>
-      <c r="R12" s="18" t="n"/>
-      <c r="S12" s="18" t="n"/>
       <c r="T12" s="18" t="n"/>
       <c r="U12" s="18" t="n"/>
     </row>
@@ -1670,7 +1705,7 @@
       <c r="E13" s="19" t="n"/>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>10. Перевод абонентов этапа 1 на единый план нумерации</t>
+          <t>10. Консолидация мелких АТС этапа 1</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -1680,20 +1715,17 @@
       </c>
       <c r="H13" s="20" t="n"/>
       <c r="I13" s="19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
           <t>Организационный поток, идёт силами второго исполнителя. Переходный период не менее месяца, старый номер остаётся рабочим.</t>
         </is>
       </c>
-      <c r="P13" s="18" t="n"/>
-      <c r="Q13" s="18" t="n"/>
       <c r="R13" s="18" t="n"/>
       <c r="S13" s="18" t="n"/>
       <c r="T13" s="18" t="n"/>
       <c r="U13" s="18" t="n"/>
-      <c r="V13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="19" t="n"/>
@@ -1701,7 +1733,7 @@
       <c r="E14" s="19" t="n"/>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>11. Воронежский вынос</t>
+          <t>11. Перевод абонентов этапа 1 на единый план нумерации</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -1711,15 +1743,20 @@
       </c>
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
           <t>445 абонентов — треть периметра — переводятся в конце графика, запаса после них не остаётся. Зато с вводом Воронежа узлов становится семь: число нечётное, арбитр в итоговой схеме не нужен.</t>
         </is>
       </c>
-      <c r="W14" s="18" t="n"/>
-      <c r="X14" s="18" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="18" t="n"/>
+      <c r="U14" s="18" t="n"/>
+      <c r="V14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="19" t="n"/>
@@ -1727,7 +1764,7 @@
       <c r="E15" s="19" t="n"/>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>12. Консолидация воронежских АТС</t>
+          <t>12. Воронежский вынос</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -1737,11 +1774,11 @@
       </c>
       <c r="H15" s="20" t="n"/>
       <c r="I15" s="19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="19" t="inlineStr"/>
+      <c r="W15" s="18" t="n"/>
       <c r="X15" s="18" t="n"/>
-      <c r="Y15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="19" t="n"/>
@@ -1749,7 +1786,7 @@
       <c r="E16" s="19" t="n"/>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>13. Перевод воронежских абонентов на единый план нумерации</t>
+          <t>13. Консолидация воронежских АТС</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -1768,46 +1805,68 @@
       </c>
       <c r="X16" s="18" t="n"/>
       <c r="Y16" s="18" t="n"/>
-      <c r="Z16" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="8" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>14. Перевод воронежских абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="19" t="inlineStr"/>
+      <c r="X17" s="18" t="n"/>
+      <c r="Y17" s="18" t="n"/>
+      <c r="Z17" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Статусы открытых/закрытых проектов:</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="21" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>норма</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>отклонений по плановым срокам основных вех/трудозатратам нет</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="F21" s="22" t="inlineStr">
+    <row r="22">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>внимание</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>есть вероятность отклонений по плановым срокам основных вех/трудозатратам, которые могут повлиять на изменение плановых сроков/трудозатрат проекта</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="F22" s="23" t="inlineStr">
+    <row r="23">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>тревога</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>есть отклонения по плановым срокам основных вех/трудозатратам</t>
         </is>
@@ -1817,7 +1876,7 @@
   <mergeCells count="7">
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="O1:R1"/>
-    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G23:J23"/>
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="K1:N1"/>
